--- a/www/download/IND.gdp.s.mv.rpO1.xlsx
+++ b/www/download/IND.gdp.s.mv.rpO1.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>8932705.948</t>
+          <t>8932705948179.4</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8846421.495</t>
+          <t>8846421494859.22</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>9030551.226</t>
+          <t>9030551225662.13</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>8983940.938</t>
+          <t>8983940937859.16</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>10326593.359</t>
+          <t>10326593358892.6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>11371981.348</t>
+          <t>11371981348109</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>11301074.832</t>
+          <t>11301074831723.7</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>12304933.602</t>
+          <t>12304933602203.5</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>14873325.041</t>
+          <t>14873325040690.5</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>15191367.838</t>
+          <t>15191367837965.3</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>15177277.797</t>
+          <t>15177277797165.3</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>14092015.182</t>
+          <t>14092015181835.8</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>12849524.403</t>
+          <t>12849524402568</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>10602432.763</t>
+          <t>10602432763088.6</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>10146486.113</t>
+          <t>10146486112779.5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>6758751.032</t>
+          <t>6758751031682.26</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5873703.004</t>
+          <t>5873703003740.59</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>5429940.045</t>
+          <t>5429940045287.89</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>6213616.616</t>
+          <t>6213616615876.72</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>6637622.876</t>
+          <t>6637622876075.15</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6858667.583</t>
+          <t>6858667582734.06</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>7229423.002</t>
+          <t>7229423001605.82</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>7458640.763</t>
+          <t>7458640762957.11</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>8652413.534</t>
+          <t>8652413533748.4</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>8137240.539</t>
+          <t>8137240539411.92</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>7435553.161</t>
+          <t>7435553161361.15</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>6730609.556</t>
+          <t>6730609556267.05</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>5790322.408</t>
+          <t>5790322408114.74</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>4916017.896</t>
+          <t>4916017896217.39</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>4573551.97</t>
+          <t>4573551969964.61</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>7017027.634</t>
+          <t>7017027634283.78</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6132152.451</t>
+          <t>6132152450820.22</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>5768452.288</t>
+          <t>5768452287681.89</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>6584247.306</t>
+          <t>6584247305514.24</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>7112111.99</t>
+          <t>7112111989711.91</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7353765.192</t>
+          <t>7353765192245.99</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>8008437.027</t>
+          <t>8008437027359.66</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>8359164.263</t>
+          <t>8359164263319.32</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>9689217.813</t>
+          <t>9689217812643.92</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>9147410.606</t>
+          <t>9147410606101.04</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>8296318.045</t>
+          <t>8296318045389.17</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>7515738.497</t>
+          <t>7515738496814.89</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>6449481.239</t>
+          <t>6449481239113.79</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>5453551.806</t>
+          <t>5453551805771.16</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>5138133.868</t>
+          <t>5138133868355.01</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>393801.814</t>
+          <t>393801814403.427</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>338992.411</t>
+          <t>338992410822.832</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>275453.553</t>
+          <t>275453552886.233</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>370828.536</t>
+          <t>370828536326.65</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>384732.738</t>
+          <t>384732738138.652</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>393283.277</t>
+          <t>393283276944.161</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>436139.803</t>
+          <t>436139803488.833</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>465244.725</t>
+          <t>465244724917.302</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>560539.246</t>
+          <t>560539246074.219</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>557456.942</t>
+          <t>557456942151.931</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>538064.856</t>
+          <t>538064856391.962</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>509612.313</t>
+          <t>509612312637.838</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>501499.287</t>
+          <t>501499287122.926</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>471365.003</t>
+          <t>471365003462.727</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>465098.327</t>
+          <t>465098327423.085</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>13884313.625</t>
+          <t>13884313625270.9</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>13610028.471</t>
+          <t>13610028470891.7</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>14335859.187</t>
+          <t>14335859186899.5</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>15671646.739</t>
+          <t>15671646738560</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>11499188.304</t>
+          <t>11499188304109.3</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>14937980.797</t>
+          <t>14937980797417.3</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>13473938.317</t>
+          <t>13473938316776.3</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>11971832.185</t>
+          <t>11971832184582.5</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>12163050.245</t>
+          <t>12163050245250.9</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>12316653.125</t>
+          <t>12316653125486.7</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>14811657.396</t>
+          <t>14811657396137</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>15776339.01</t>
+          <t>15776339009804.5</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>17550820.376</t>
+          <t>17550820375976.9</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>16053535.89</t>
+          <t>16053535890277.5</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>15789919.06</t>
+          <t>15789919060117</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>13103728.197</t>
+          <t>13103728197092.1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>12200573.331</t>
+          <t>12200573330668.5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>13079890.113</t>
+          <t>13079890113181.7</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>14327529.815</t>
+          <t>14327529815160.7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>16242737.131</t>
+          <t>16242737131350.9</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>20082863.558</t>
+          <t>20082863558466.8</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>21500516.229</t>
+          <t>21500516229388.3</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>21136579.728</t>
+          <t>21136579727727.1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>23615986.348</t>
+          <t>23615986348290.7</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>22676230.205</t>
+          <t>22676230205157.8</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>22940908.434</t>
+          <t>22940908433875.4</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>22592119.45</t>
+          <t>22592119450232.1</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>18644100.322</t>
+          <t>18644100322417.3</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>14919421.681</t>
+          <t>14919421681021.8</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>12959042.363</t>
+          <t>12959042363103.7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>25792038.671</t>
+          <t>25792038671041.8</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>27452485.45</t>
+          <t>27452485449608.9</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>31304969.055</t>
+          <t>31304969054934</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>36559303.01</t>
+          <t>36559303010171.6</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>40739038.784</t>
+          <t>40739038783812</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>50323106.684</t>
+          <t>50323106684369.2</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>57817991.62</t>
+          <t>57817991620200.6</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>59162031.136</t>
+          <t>59162031136230.4</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>62324939.575</t>
+          <t>62324939575245.6</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>61754207.979</t>
+          <t>61754207979031.3</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>62723134.46</t>
+          <t>62723134460239.7</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>62891703.22</t>
+          <t>62891703220363.5</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>58869550.342</t>
+          <t>58869550341791</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>57135796.756</t>
+          <t>57135796755571</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>60487441.135</t>
+          <t>60487441134538.5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>186474.428</t>
+          <t>186474427912.406</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>171903.661</t>
+          <t>171903660618.448</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>173124.429</t>
+          <t>173124429499.912</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>201515.966</t>
+          <t>201515965683.985</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>218221.917</t>
+          <t>218221916611.003</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>229931.292</t>
+          <t>229931291514.888</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>247244.025</t>
+          <t>247244024938.809</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>266503.805</t>
+          <t>266503804841.754</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>335888.153</t>
+          <t>335888153233.149</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>330034.77</t>
+          <t>330034769792.258</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>311061.736</t>
+          <t>311061735791.919</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>289737.99</t>
+          <t>289737989797.985</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>249431.987</t>
+          <t>249431987022.87</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>219669.851</t>
+          <t>219669851414.774</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>215286.587</t>
+          <t>215286586613.414</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1062353.778</t>
+          <t>1062353778021.48</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1446724.218</t>
+          <t>1446724218049.11</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1402355.433</t>
+          <t>1402355432517.79</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1653538.375</t>
+          <t>1653538374709.78</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1709810.657</t>
+          <t>1709810656833.15</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1845751.927</t>
+          <t>1845751926591.93</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2171625.605</t>
+          <t>2171625604796.9</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2618934.75</t>
+          <t>2618934749524.09</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>3075423.112</t>
+          <t>3075423112029.88</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2995411.253</t>
+          <t>2995411252937.65</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>3011600.606</t>
+          <t>3011600605574.42</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2946037.372</t>
+          <t>2946037371840.58</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2671723.481</t>
+          <t>2671723481188.28</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2520647.95</t>
+          <t>2520647949582.82</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2097825.317</t>
+          <t>2097825316511.91</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>70033732.715</t>
+          <t>70033732714598.3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>60550779.393</t>
+          <t>60550779393303.7</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>55347339.394</t>
+          <t>55347339394099.8</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>62418678.192</t>
+          <t>62418678191602.4</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>65586830.607</t>
+          <t>65586830607089</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>67944594.132</t>
+          <t>67944594131981.2</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>71665203.081</t>
+          <t>71665203081333.1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>72741634.367</t>
+          <t>72741634367414.4</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>83107046.029</t>
+          <t>83107046028504.4</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>77162124.453</t>
+          <t>77162124453044.8</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>68562373.295</t>
+          <t>68562373295269.8</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>60728448.904</t>
+          <t>60728448904495.2</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>50850341.099</t>
+          <t>50850341098789</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>41957776.65</t>
+          <t>41957776649829.7</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>38885481.739</t>
+          <t>38885481738527.5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4616988.643</t>
+          <t>4616988643355.22</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>4220899.536</t>
+          <t>4220899535806.89</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>4052213.599</t>
+          <t>4052213598903.36</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>4732159.987</t>
+          <t>4732159987301.97</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>5131991.011</t>
+          <t>5131991011171.89</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>5344591.121</t>
+          <t>5344591120624.55</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5760355.304</t>
+          <t>5760355304114.84</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>6073087.82</t>
+          <t>6073087820249.8</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>7099465.944</t>
+          <t>7099465944104.34</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>6707140.33</t>
+          <t>6707140330379.32</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>6210473.375</t>
+          <t>6210473374723.18</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>5662713.33</t>
+          <t>5662713329683.28</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>4881490.06</t>
+          <t>4881490059552.81</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>4112731.04</t>
+          <t>4112731039900.72</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>3907131.442</t>
+          <t>3907131442436.91</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>15240207.725</t>
+          <t>15240207724560.8</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>14321492.063</t>
+          <t>14321492063054.4</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>13823623.355</t>
+          <t>13823623355012.3</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>16134824.932</t>
+          <t>16134824932240.1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>17782653.177</t>
+          <t>17782653177293.2</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>18551107.553</t>
+          <t>18551107553143.9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>20785278.808</t>
+          <t>20785278808034.3</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>22386331.711</t>
+          <t>22386331711363.5</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>27273851.697</t>
+          <t>27273851697148.9</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>26676197.905</t>
+          <t>26676197905337.2</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>25632864.087</t>
+          <t>25632864087155.2</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>23917937.034</t>
+          <t>23917937034363</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>21129014.321</t>
+          <t>21129014320732.2</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>17575384.193</t>
+          <t>17575384193102.8</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>15580705.547</t>
+          <t>15580705547417.3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>106670.878</t>
+          <t>106670878422.128</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>114104.671</t>
+          <t>114104671401.546</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>120876.294</t>
+          <t>120876293640.146</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>146366.823</t>
+          <t>146366822937.086</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>151906.125</t>
+          <t>151906125457.108</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>167793.2</t>
+          <t>167793200289.528</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>189815.895</t>
+          <t>189815894566.835</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>214321.697</t>
+          <t>214321696719.042</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>272211.038</t>
+          <t>272211038433.927</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>282443.809</t>
+          <t>282443809030.911</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>291856.199</t>
+          <t>291856199087.11</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>299117.583</t>
+          <t>299117583267.67</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>307628.176</t>
+          <t>307628175682.07</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>278519.65</t>
+          <t>278519650261.22</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>215641.441</t>
+          <t>215641440839.815</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>3792794.362</t>
+          <t>3792794362175.59</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3397912.5</t>
+          <t>3397912499637.15</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>3332195.272</t>
+          <t>3332195272449.31</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>3880330.31</t>
+          <t>3880330310271.93</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>4207349.283</t>
+          <t>4207349283196.02</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4434753.86</t>
+          <t>4434753860144.71</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4868740.076</t>
+          <t>4868740075991.36</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>5054162.351</t>
+          <t>5054162351260.23</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>5875286.966</t>
+          <t>5875286966192.92</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>5631562.389</t>
+          <t>5631562389421.22</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>5283128.834</t>
+          <t>5283128833714.22</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>4812372.775</t>
+          <t>4812372774703.78</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>4163611.734</t>
+          <t>4163611733937.31</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>3560732.931</t>
+          <t>3560732930564.77</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>3218042.899</t>
+          <t>3218042899444.42</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>35422536.501</t>
+          <t>35422536500829.8</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>31844150.98</t>
+          <t>31844150979972</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>29796725.669</t>
+          <t>29796725668753.1</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>33782470.284</t>
+          <t>33782470284402.9</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>36357732.433</t>
+          <t>36357732433183.3</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>37810266.865</t>
+          <t>37810266864668.5</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>40804153.177</t>
+          <t>40804153177050.6</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>43196279.479</t>
+          <t>43196279479382.6</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>50705705.173</t>
+          <t>50705705173315.8</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>48298621.874</t>
+          <t>48298621874445.7</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>44681274.968</t>
+          <t>44681274967859.4</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>40278256.264</t>
+          <t>40278256264128.1</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>34487065.806</t>
+          <t>34487065805858.2</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>28718325</t>
+          <t>28718324999600.3</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>26441556.286</t>
+          <t>26441556285902.1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>29621016.281</t>
+          <t>29621016281472.1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>27368040.236</t>
+          <t>27368040236230.4</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>31287931.399</t>
+          <t>31287931399119.1</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>37606327.128</t>
+          <t>37606327127538.9</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>41524615.185</t>
+          <t>41524615185387.8</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>47094623.004</t>
+          <t>47094623004038.4</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>49997622.605</t>
+          <t>49997622605110.1</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>52463379.316</t>
+          <t>52463379315990.2</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>57358898.412</t>
+          <t>57358898411760.4</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>56559909.278</t>
+          <t>56559909277539.9</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>53152791.018</t>
+          <t>53152791017834.7</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>48918524.468</t>
+          <t>48918524468112.5</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>42001349.275</t>
+          <t>42001349275354</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>29914246.617</t>
+          <t>29914246616961</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>24967604.621</t>
+          <t>24967604621280.9</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2405540.232</t>
+          <t>2405540232382.61</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2286068.634</t>
+          <t>2286068634150.81</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2351537.824</t>
+          <t>2351537823805.46</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2649550.035</t>
+          <t>2649550035463.57</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2998285.097</t>
+          <t>2998285096733.52</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3114497.918</t>
+          <t>3114497917834.25</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3294680.36</t>
+          <t>3294680359594.57</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>3949510.687</t>
+          <t>3949510686674.72</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>4924745.001</t>
+          <t>4924745001176.08</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>4775833.511</t>
+          <t>4775833511165.89</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>4448319.174</t>
+          <t>4448319174223.39</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>4238506.346</t>
+          <t>4238506346409.69</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>3664647.76</t>
+          <t>3664647759710.2</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>3009095.261</t>
+          <t>3009095261489.71</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2878084.421</t>
+          <t>2878084420777.71</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1222523.554</t>
+          <t>1222523553579.55</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1069467.716</t>
+          <t>1069467715675.26</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1113812.458</t>
+          <t>1113812457565.59</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1246961.935</t>
+          <t>1246961935227.82</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1326941.97</t>
+          <t>1326941970485.29</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1537968.039</t>
+          <t>1537968039251.1</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1774625.546</t>
+          <t>1774625545981.35</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2111383.37</t>
+          <t>2111383369949.8</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2521402.883</t>
+          <t>2521402883393.69</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2544544.379</t>
+          <t>2544544378613.58</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2456827.299</t>
+          <t>2456827299428.9</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2090343.914</t>
+          <t>2090343914027.86</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>1870355.62</t>
+          <t>1870355620174.92</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>1540236.802</t>
+          <t>1540236802002.95</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1200156.809</t>
+          <t>1200156809070.67</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>5488810.2</t>
+          <t>5488810200004.59</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>5868625.638</t>
+          <t>5868625638139.24</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>6247208.483</t>
+          <t>6247208482700.07</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2820983.685</t>
+          <t>2820983684616.48</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>4719313.516</t>
+          <t>4719313515792.29</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>5754081.971</t>
+          <t>5754081971288.08</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>5508592.142</t>
+          <t>5508592141791.6</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>6292893.513</t>
+          <t>6292893513492.38</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>7061093.634</t>
+          <t>7061093634480.39</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>6035729.316</t>
+          <t>6035729315711.55</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>5561060.889</t>
+          <t>5561060889001.59</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>6472546.927</t>
+          <t>6472546926530.78</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>5727144.918</t>
+          <t>5727144918105.89</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>5252808.408</t>
+          <t>5252808407650.21</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>5499618.833</t>
+          <t>5499618833226.54</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>10337756.127</t>
+          <t>10337756126839.7</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>9153747.148</t>
+          <t>9153747148311.97</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>10684313.408</t>
+          <t>10684313407609.5</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>11527405.559</t>
+          <t>11527405558560.9</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>12870298.915</t>
+          <t>12870298914950.1</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>15337513.664</t>
+          <t>15337513663942.1</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>17084384.043</t>
+          <t>17084384042687.9</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>16883762.432</t>
+          <t>16883762432374.8</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>18509077.869</t>
+          <t>18509077869137.6</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>17901950.584</t>
+          <t>17901950584320.7</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>18726048.966</t>
+          <t>18726048965615.7</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>18008908.777</t>
+          <t>18008908777161.4</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>16956295.135</t>
+          <t>16956295135141.4</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>13762105.836</t>
+          <t>13762105836389.9</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>14075306.439</t>
+          <t>14075306438967.7</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1825819.828</t>
+          <t>1825819828477.17</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1754903.03</t>
+          <t>1754903030498.4</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1906030.4</t>
+          <t>1906030400069.3</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2255919.532</t>
+          <t>2255919532411.33</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2568417.827</t>
+          <t>2568417827156.26</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2913328.048</t>
+          <t>2913328047983.21</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3384621.928</t>
+          <t>3384621928284.4</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>3653445.415</t>
+          <t>3653445415182.74</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>4520180.439</t>
+          <t>4520180438557.41</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>4557300.353</t>
+          <t>4557300353024.81</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>4514146.139</t>
+          <t>4514146139429.64</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>4342861.189</t>
+          <t>4342861189391.31</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>3851191.572</t>
+          <t>3851191571839.9</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>3248668.085</t>
+          <t>3248668085174.01</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2798862.831</t>
+          <t>2798862830780.88</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>29167498.466</t>
+          <t>29167498465818.3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>29386047.56</t>
+          <t>29386047560467.5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>29363909.598</t>
+          <t>29363909598114.7</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>32073193.065</t>
+          <t>32073193065491.5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>33965541.708</t>
+          <t>33965541708100</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>34931176.513</t>
+          <t>34931176512929.2</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>37963033.666</t>
+          <t>37963033666324.2</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>40032091.194</t>
+          <t>40032091193539.4</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>47387703.813</t>
+          <t>47387703812701.4</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>44879582.242</t>
+          <t>44879582241802.5</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>41594634.778</t>
+          <t>41594634778428.6</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>37638604.553</t>
+          <t>37638604553417.4</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>31984216.856</t>
+          <t>31984216856038</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>26608873.888</t>
+          <t>26608873887532</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>23951292.231</t>
+          <t>23951292230935.2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>130612182.592</t>
+          <t>130612182591979</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>101368280.148</t>
+          <t>101368280147558</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>96798992.096</t>
+          <t>96798992095782.8</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>98180729.718</t>
+          <t>98180729717805.7</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>120450798.003</t>
+          <t>120450798003297</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>145077551.897</t>
+          <t>145077551896815</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>134546746.952</t>
+          <t>134546746951825</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>121896719.769</t>
+          <t>121896719769372</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>123377194.802</t>
+          <t>123377194802266</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>110772641.925</t>
+          <t>110772641925189</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>96306046.466</t>
+          <t>96306046465576.9</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>78554797.241</t>
+          <t>78554797240589.1</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>59105775.148</t>
+          <t>59105775148415</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>48635919.717</t>
+          <t>48635919717166.9</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>48278803.797</t>
+          <t>48278803797239.4</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>19162007.8</t>
+          <t>19162007799813.7</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>19053207.318</t>
+          <t>19053207317633.4</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>18310944.931</t>
+          <t>18310944930775</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>13238797.283</t>
+          <t>13238797283045.2</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>17014851.168</t>
+          <t>17014851168181</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>22240873.779</t>
+          <t>22240873778915.7</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>23356270.816</t>
+          <t>23356270815981.1</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>25245019.15</t>
+          <t>25245019150008.3</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>27507082.559</t>
+          <t>27507082559422.2</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>25741233.882</t>
+          <t>25741233882368.2</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>27512872.614</t>
+          <t>27512872614468.5</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>26422867.459</t>
+          <t>26422867459304.7</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>21553148.532</t>
+          <t>21553148531652.1</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>14530492.323</t>
+          <t>14530492322654.8</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>12699320.161</t>
+          <t>12699320161235</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>152819.368</t>
+          <t>152819367899.031</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>183949.658</t>
+          <t>183949658463.999</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>239939.109</t>
+          <t>239939108902.46</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>298250.765</t>
+          <t>298250765125.854</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>317394.11</t>
+          <t>317394110184.407</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>355675.192</t>
+          <t>355675191721.762</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>400155.805</t>
+          <t>400155804934.83</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>426279.937</t>
+          <t>426279936997.4</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>535586.061</t>
+          <t>535586061435.94</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>567027.89</t>
+          <t>567027890478.131</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>577916.875</t>
+          <t>577916874607.403</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>587217.296</t>
+          <t>587217296111.948</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>576185.211</t>
+          <t>576185211166.714</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>521469.624</t>
+          <t>521469624251.2</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>404148.773</t>
+          <t>404148773316.43</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>383464.923</t>
+          <t>383464923088.08</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>336985.91</t>
+          <t>336985910364.396</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>318329.116</t>
+          <t>318329115861.928</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>365750.483</t>
+          <t>365750483171.323</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>401729.075</t>
+          <t>401729075237.239</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>439719.234</t>
+          <t>439719233781.783</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>491885.488</t>
+          <t>491885488440.516</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>536834.49</t>
+          <t>536834489588.479</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>652996.256</t>
+          <t>652996255872.109</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>637222.246</t>
+          <t>637222246077.675</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>607279.397</t>
+          <t>607279396625.884</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>554448.698</t>
+          <t>554448697731.122</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>480512.818</t>
+          <t>480512817782.686</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>433850.737</t>
+          <t>433850737380.009</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>430363.414</t>
+          <t>430363413728.034</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>124319.598</t>
+          <t>124319598134.481</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>125323.96</t>
+          <t>125323959829.946</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>149324.122</t>
+          <t>149324122035.769</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>167115.107</t>
+          <t>167115106508.023</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>181296.528</t>
+          <t>181296528461.619</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>205847.574</t>
+          <t>205847574154.856</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>226064.397</t>
+          <t>226064396796.727</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>236369.61</t>
+          <t>236369609813.325</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>275623.577</t>
+          <t>275623576726.958</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>275135.644</t>
+          <t>275135643987.361</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>313427.433</t>
+          <t>313427432839.379</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>347520.869</t>
+          <t>347520868794.246</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>391689.008</t>
+          <t>391689007826.115</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>367525.136</t>
+          <t>367525135678.825</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>229998.205</t>
+          <t>229998204980.984</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>4931075.747</t>
+          <t>4931075746988.09</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>4881272.967</t>
+          <t>4881272966635.85</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>6348480.744</t>
+          <t>6348480743781.08</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>7879876.638</t>
+          <t>7879876638414.12</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>9963185.104</t>
+          <t>9963185104058.32</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>13915156.899</t>
+          <t>13915156898541.2</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>16682225.169</t>
+          <t>16682225168560.9</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>16580562.525</t>
+          <t>16580562525416.8</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>15094379.395</t>
+          <t>15094379394649.9</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>12965308.264</t>
+          <t>12965308263704.7</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>12842537.438</t>
+          <t>12842537438163.7</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>11941625.693</t>
+          <t>11941625692856.4</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>9557191.568</t>
+          <t>9557191567585.23</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>7540563.972</t>
+          <t>7540563972378.57</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>5904949.833</t>
+          <t>5904949833110.75</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>79216.672</t>
+          <t>79216672485.6987</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>75282.304</t>
+          <t>75282303962.1885</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>76394.826</t>
+          <t>76394825745.2168</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>91075.039</t>
+          <t>91075038552.9108</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>100216.535</t>
+          <t>100216534815.412</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>109516.879</t>
+          <t>109516879376.548</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>122580.589</t>
+          <t>122580588846.667</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>131623.481</t>
+          <t>131623481030.617</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>148147.555</t>
+          <t>148147554814.033</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>135319.237</t>
+          <t>135319237435.184</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>123791.909</t>
+          <t>123791908552.99</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>111409.301</t>
+          <t>111409300730.641</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>94169.943</t>
+          <t>94169942903.6294</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>97310.302</t>
+          <t>97310302399.0712</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>84669.641</t>
+          <t>84669640576.4967</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>9841295.648</t>
+          <t>9841295648029.58</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>8753395.888</t>
+          <t>8753395887786.42</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>8305969.89</t>
+          <t>8305969889555.89</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>9707152.115</t>
+          <t>9707152114647.21</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>10727317.51</t>
+          <t>10727317510053.3</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>11468426.871</t>
+          <t>11468426871394.9</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>12679090.495</t>
+          <t>12679090495372.1</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>13628239.23</t>
+          <t>13628239229864.7</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>16092628.061</t>
+          <t>16092628060551.9</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>15252992.775</t>
+          <t>15252992774936.9</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>13826979.646</t>
+          <t>13826979645581.8</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>12418176.329</t>
+          <t>12418176328985.2</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>10658660.628</t>
+          <t>10658660628433.2</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>9063969.938</t>
+          <t>9063969938270.55</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>8582030.293</t>
+          <t>8582030293424.93</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>7308960.903</t>
+          <t>7308960903290.08</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>7153181.379</t>
+          <t>7153181379386.12</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>7483154.359</t>
+          <t>7483154358575.5</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>9551030.916</t>
+          <t>9551030916115.32</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>10314984.167</t>
+          <t>10314984166621.3</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>8846621.042</t>
+          <t>8846621041772.6</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>9312941.213</t>
+          <t>9312941213035.73</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>8507953.261</t>
+          <t>8507953260723.47</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>8343814.267</t>
+          <t>8343814266827.46</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>7673815.211</t>
+          <t>7673815210590.79</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>8126789.715</t>
+          <t>8126789715252.38</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>7375254.66</t>
+          <t>7375254660145.64</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>6683171.706</t>
+          <t>6683171705527.1</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>6508473.719</t>
+          <t>6508473718638.19</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>5037390.225</t>
+          <t>5037390225111.96</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2830280.558</t>
+          <t>2830280558106.89</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2713229.429</t>
+          <t>2713229428575.58</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2728682.166</t>
+          <t>2728682166053.48</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>3236609.203</t>
+          <t>3236609203249</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>3581626.035</t>
+          <t>3581626034899.38</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>3885528.448</t>
+          <t>3885528447638.34</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>4288085.698</t>
+          <t>4288085697774.46</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>4555166.603</t>
+          <t>4555166602981.89</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>5250191.669</t>
+          <t>5250191669245.8</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>4971447.019</t>
+          <t>4971447019063.53</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>4572416.373</t>
+          <t>4572416373345.79</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>4067005.402</t>
+          <t>4067005401606.59</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>3456449.624</t>
+          <t>3456449623603.5</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2851931.824</t>
+          <t>2851931823638.06</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2631579.472</t>
+          <t>2631579472149.69</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1314123.044</t>
+          <t>1314123043657.88</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1198645.734</t>
+          <t>1198645733919.22</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1050921.361</t>
+          <t>1050921361170.26</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1707095.773</t>
+          <t>1707095772920.58</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1345095.28</t>
+          <t>1345095279673.16</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>1783780.138</t>
+          <t>1783780137808.89</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2420458.86</t>
+          <t>2420458860319.67</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2605387.447</t>
+          <t>2605387446744.72</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>3219360.722</t>
+          <t>3219360722205.91</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2494141.303</t>
+          <t>2494141303433.41</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>3444498.354</t>
+          <t>3444498353803.47</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>3682239.817</t>
+          <t>3682239816549.23</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>3586733.693</t>
+          <t>3586733692947.64</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>3457386.897</t>
+          <t>3457386897043.51</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2531431.216</t>
+          <t>2531431216085.31</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>8511159.708</t>
+          <t>8511159708033.91</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>9353229.134</t>
+          <t>9353229134115.56</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>9764429.986</t>
+          <t>9764429985707.54</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>8276700.64</t>
+          <t>8276700639558.57</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>5330807.934</t>
+          <t>5330807933674.48</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>7914527.724</t>
+          <t>7914527724142.32</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>9782490.462</t>
+          <t>9782490461791.11</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>11336890.522</t>
+          <t>11336890521759.9</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>13041270.524</t>
+          <t>13041270523660.5</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>14284665.362</t>
+          <t>14284665362362.6</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>16187682.227</t>
+          <t>16187682227110.3</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>17726899.652</t>
+          <t>17726899652283.4</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>17277827.46</t>
+          <t>17277827460053.2</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>16371482.342</t>
+          <t>16371482342246.2</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>11672455.858</t>
+          <t>11672455858339</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>339195.61</t>
+          <t>339195609702.663</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>334649.833</t>
+          <t>334649833290.711</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>367373.434</t>
+          <t>367373434139.161</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>420369.762</t>
+          <t>420369761986.435</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>391337.823</t>
+          <t>391337823354.708</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>444895.864</t>
+          <t>444895864256.9</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>477081.162</t>
+          <t>477081162484.911</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>526401.053</t>
+          <t>526401053037.138</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>690273.143</t>
+          <t>690273143251.959</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>708782.672</t>
+          <t>708782672102.06</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>709223.483</t>
+          <t>709223482502.625</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>710566.347</t>
+          <t>710566346875.787</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>703338.419</t>
+          <t>703338419209.315</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>697389.323</t>
+          <t>697389322888.55</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>648081.667</t>
+          <t>648081667081.062</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>790501.549</t>
+          <t>790501548774.639</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>680503.63</t>
+          <t>680503630317.789</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>660483.386</t>
+          <t>660483386407.546</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>760921.708</t>
+          <t>760921707862.806</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>813049.815</t>
+          <t>813049814538.207</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>850003.04</t>
+          <t>850003039943.819</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>924627.918</t>
+          <t>924627918003.975</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>977507.99</t>
+          <t>977507989912.665</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>1142961.811</t>
+          <t>1142961810862.82</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>1113928.693</t>
+          <t>1113928692967.48</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>1053956.72</t>
+          <t>1053956720383.16</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>962265.802</t>
+          <t>962265802088.864</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>857052.389</t>
+          <t>857052389228.042</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>760823.238</t>
+          <t>760823237838.726</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>687107.4</t>
+          <t>687107399898.498</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>6557506.177</t>
+          <t>6557506176913.54</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>6666799.128</t>
+          <t>6666799127611.85</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>6350117.109</t>
+          <t>6350117108794.42</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>7116036.116</t>
+          <t>7116036115574.08</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>7616616.176</t>
+          <t>7616616176036.46</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>8613437.652</t>
+          <t>8613437651699.86</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>8776748.548</t>
+          <t>8776748548282.69</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>9317745.716</t>
+          <t>9317745715720.86</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>11069193.282</t>
+          <t>11069193281939.4</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>10501201.49</t>
+          <t>10501201490044</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>9517093.229</t>
+          <t>9517093229059.91</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>8496442.721</t>
+          <t>8496442720925.4</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>7509931.718</t>
+          <t>7509931717757.17</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>6005915.474</t>
+          <t>6005915473931.99</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>4979076.885</t>
+          <t>4979076884953.42</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>3852890.169</t>
+          <t>3852890168650.75</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>4090985.181</t>
+          <t>4090985180964.83</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>4754112.886</t>
+          <t>4754112886393.83</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>5925628.187</t>
+          <t>5925628186819.33</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>6500605.201</t>
+          <t>6500605200925.6</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>7548315.045</t>
+          <t>7548315044825.17</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>5607571.865</t>
+          <t>5607571865265.25</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>5971650.192</t>
+          <t>5971650191762</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>7319634.375</t>
+          <t>7319634375455.61</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>7850322.387</t>
+          <t>7850322386814.2</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>9069920.844</t>
+          <t>9069920843794.96</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>8194156.071</t>
+          <t>8194156070795.74</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>7469213.143</t>
+          <t>7469213143011.88</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>6368117.852</t>
+          <t>6368117851924.28</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>5155804.968</t>
+          <t>5155804968015.27</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>6379691.383</t>
+          <t>6379691382851.72</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>5897448.472</t>
+          <t>5897448472255.43</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>6109009.218</t>
+          <t>6109009218412.09</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>6048423.88</t>
+          <t>6048423880447.21</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>6951806.014</t>
+          <t>6951806013806.68</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>8254150.902</t>
+          <t>8254150901960.7</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>7976637.466</t>
+          <t>7976637466081.6</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>7254430.78</t>
+          <t>7254430780212.23</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>6981036.437</t>
+          <t>6981036436553.39</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>6144912.284</t>
+          <t>6144912283931</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>6069025.009</t>
+          <t>6069025008858.26</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>5476534.817</t>
+          <t>5476534817420.7</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>4261638.893</t>
+          <t>4261638892961.59</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>3359381.624</t>
+          <t>3359381624387.78</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2954610.076</t>
+          <t>2954610075501.65</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>131806029.291</t>
+          <t>131806029290546</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>123110161.477</t>
+          <t>123110161477315</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>135739614.067</t>
+          <t>135739614066650</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>164038178.548</t>
+          <t>164038178548416</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>188592811.082</t>
+          <t>188592811081844</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>231174927.472</t>
+          <t>231174927472467</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>252713591.247</t>
+          <t>252713591247496</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>248718636.252</t>
+          <t>248718636251877</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>247023806.968</t>
+          <t>247023806968239</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>217514735.678</t>
+          <t>217514735678038</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>202513864.857</t>
+          <t>202513864857455</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>186678048.474</t>
+          <t>186678048474265</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>146433771.329</t>
+          <t>146433771328731</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>112907399.321</t>
+          <t>112907399321226</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>103724014.708</t>
+          <t>103724014707811</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>56704821.218</t>
+          <t>56704821217850.9</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>55166197.675</t>
+          <t>55166197675336.5</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>57353454.387</t>
+          <t>57353454386708.4</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>59482125.054</t>
+          <t>59482125053564.5</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>66224482.967</t>
+          <t>66224482967114</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>84350552.123</t>
+          <t>84350552123029</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>87712020.116</t>
+          <t>87712020116141.5</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>85432649.606</t>
+          <t>85432649605690.1</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>92851839.938</t>
+          <t>92851839937638.7</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>93270197.19</t>
+          <t>93270197190304.5</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>100452121.405</t>
+          <t>100452121405482</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>101728552.526</t>
+          <t>101728552525690</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>87773191.731</t>
+          <t>87773191731408.8</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>86168749.315</t>
+          <t>86168749315064.2</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>71351538.992</t>
+          <t>71351538991837.4</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>678094632.597</t>
+          <t>678094632597201</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>618551952.822</t>
+          <t>618551952822051</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>633138039.672</t>
+          <t>633138039671845</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>698333205.702</t>
+          <t>698333205701714</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>780881945.138</t>
+          <t>780881945138307</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>915813135.321</t>
+          <t>915813135320759</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>963764771.359</t>
+          <t>963764771358579</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>962682215.922</t>
+          <t>962682215922411</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>1032524473.368</t>
+          <t>1032524473367735</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>967993984.836</t>
+          <t>967993984835703</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>930188819.507</t>
+          <t>930188819507162</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>866789083.829</t>
+          <t>866789083829037</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>733880459.136</t>
+          <t>733880459136436</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>618480096.636</t>
+          <t>618480096635874</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>563479645.863</t>
+          <t>563479645863411</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>gdp.s.mv</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO1</t>
